--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="207">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Corps document</t>
+    <t>Logical model - FR LM Corps document</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,84 +250,254 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.allergiesEtHypersensibilites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-allergies-et-hypersensibilites
+    <t>fr-lm-corps-document.alerts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-alerts
 </t>
   </si>
   <si>
+    <t>Section Points de vigilance</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.allergiesAndIntolerances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-allergies-and-intolerances
+</t>
+  </si>
+  <si>
     <t>Section Allergies et hypersensibilités</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.antecedentsFamiliaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-antecedents-familiaux
+    <t>fr-lm-corps-document.problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-problems
 </t>
   </si>
   <si>
+    <t>Section Problemès Actifs</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.medicationSummary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-summary
+</t>
+  </si>
+  <si>
+    <t>Section Traitement</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.medicalDevicesAndImplants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medical-devices-and-implants
+</t>
+  </si>
+  <si>
+    <t>Section Dispositifs medicaux</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.procedures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedures
+</t>
+  </si>
+  <si>
+    <t>Section Historique des actes</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.immunisations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-immunisations
+</t>
+  </si>
+  <si>
+    <t>Section Vaccinations</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.functionalStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-functional-status
+</t>
+  </si>
+  <si>
+    <t>Section Statut fonctionnel</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.socialHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-social-history
+</t>
+  </si>
+  <si>
+    <t>Section Habitus et modes de vie</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.pregnancyHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section-pregnancy-history
+</t>
+  </si>
+  <si>
+    <t>Section Historique des grossesses</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.advanceDirectives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-advance-directives
+</t>
+  </si>
+  <si>
+    <t>Section Directives anticipées</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.observationResults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation-results
+</t>
+  </si>
+  <si>
+    <t>Section Résultats</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.carePlans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-care-plans
+</t>
+  </si>
+  <si>
+    <t>Section Plan de Soins</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.familyMedicalHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-family-medical-history
+</t>
+  </si>
+  <si>
     <t>Section Antécédents familiaux</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.antecedentsMedicaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-antecedents-medicaux
+    <t>fr-lm-corps-document.historyOfPastIllness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-history-of-past-illness
 </t>
   </si>
   <si>
     <t>Section Antécédents médicaux</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.codesAbarres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-codes-a-barres
+    <t>fr-lm-corps-document.predictableAdverseDrugReactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-predictable-adverse-drug-reaction
 </t>
   </si>
   <si>
+    <t>Section Effets indesirables</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.hazardousWorkingConditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-hazardous-working-conditions
+</t>
+  </si>
+  <si>
+    <t>Section Facteurs de risque professionnels non Codé</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.qrCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-qr-code
+</t>
+  </si>
+  <si>
     <t>Section Codes à barres</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.commentaireNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-commentaire-non-code
+    <t>fr-lm-corps-document.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-note
 </t>
   </si>
   <si>
     <t>Section Commentaire (Non-Codé)</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.cRBIOChapitre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-cr-bio-chapitre
+    <t>fr-lm-corps-document.medicationPrescriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-prescription
 </t>
   </si>
   <si>
-    <t>section Compte rendu de biologie de 1er niveau</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.cRBIOSousChapitre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-cr-bio-sous-chapitre
+    <t>Section Prescription médicaments</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.medicalDevicePrescriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medical-device-prescriptions
 </t>
   </si>
   <si>
-    <t>Section Sous-chapitre du compte rendu d'examens de biologie  (section de 2nd niveau)</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.acteImagerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-acte-imagerie
+    <t>Section Prescription de dispositifs médicaux</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.presentedForm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-presented-form
 </t>
   </si>
   <si>
-    <t>Section Acte d'imagerie</t>
+    <t>Section Document PDF-copie</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.attachments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-attachments
+</t>
+  </si>
+  <si>
+    <t>Section Documents ajoutés</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.travelHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section-travel-history
+</t>
+  </si>
+  <si>
+    <t>Section Historique des voyages</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.patientStory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-story
+</t>
+  </si>
+  <si>
+    <t>Section Récit du patient</t>
   </si>
   <si>
     <t>fr-lm-corps-document.addendum</t>
@@ -340,350 +510,160 @@
     <t>Section Addendum</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.conclusions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-conclusion-examen-imagerie
+    <t>fr-lm-corps-document.vitalSigns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-vital-signs
 </t>
   </si>
   <si>
-    <t>Section Conclusions</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.demandeExamenImagerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-demande-examen-imagerie
+    <t>Section Signes vitaux</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.resultData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-result-data
 </t>
   </si>
   <si>
+    <t>section Compte rendu de biologie de 1er niveau</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.examinationReport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-examination-report
+</t>
+  </si>
+  <si>
+    <t>Section Acte d'imagerie</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.orderInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-order-information
+</t>
+  </si>
+  <si>
     <t>Section Demande d'examen</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.comparaisonExamensImagerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-comparaison-examens-imagerie
+    <t>fr-lm-corps-document.comparisonStudy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-comparison-study
 </t>
   </si>
   <si>
     <t>Section Examen comparatif</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.expositionRadiations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-exposition-radiations
+    <t>fr-lm-corps-document.exposureInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-exposure-information
 </t>
   </si>
   <si>
     <t>Section Exposition aux radiations</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.informationsCliniques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informations-cliniques
+    <t>fr-lm-corps-document.supportingInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-supporting-information
 </t>
   </si>
   <si>
     <t>Section Informations cliniques</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.objectCatalog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-object-catalog
+    <t>fr-lm-corps-document.dicomStudyMetadata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dicom-study-metadata
 </t>
   </si>
   <si>
-    <t>Section  Object catalog</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.directivesAnticipees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-directives-anticipees
+    <t>Section object catalog</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.recommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-recommendation
 </t>
   </si>
   <si>
-    <t>Section Directives anticipées</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.dispensationMedicaments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dispensation-medicaments
+    <t>Section Recommandation</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-conclusion
 </t>
   </si>
   <si>
+    <t>Section Conclusion</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.medicationDispensations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-dispensations
+</t>
+  </si>
+  <si>
     <t>Section Dispensation médicaments</t>
   </si>
   <si>
-    <t>fr-lm-corps-document.dispositifsMedicaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dispositifs-medicaux
+    <t>fr-lm-corps-document.patientEducation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-education
 </t>
   </si>
   <si>
-    <t>Section Dispositifs medicaux</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.documentPDFCopie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-document-pdf-copie
+    <t>Section Education du patient</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.patientHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-history
 </t>
   </si>
   <si>
-    <t>Section Document PDF Copie</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.documentsAjoutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-documents-ajoutes
+    <t>Section Historique du patient</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.reasonForReferral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-reason-for-referral
 </t>
   </si>
   <si>
-    <t>Section Documents ajoutés</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.educationPatient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-education-patient
+    <t>Section Raison de la recommandation</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.courseOfEncounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-course-of-encounter
 </t>
   </si>
   <si>
-    <t>Section Education du patient</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.effetsIndesirables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-effets-indesirables
-</t>
-  </si>
-  <si>
-    <t>Section Effets indesirables</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.facteursDeRisqueProfessionnelsNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-facteurs-de-risque-professionnels-non-code
-</t>
-  </si>
-  <si>
-    <t>Section Facteurs de risque professionnels non Codé</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.fonctionsPhysiques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-fonctions-physiques
-</t>
-  </si>
-  <si>
-    <t>Section Fonctions physiques</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.habitusModeDeVie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-habitus-mode-de-vie
-</t>
-  </si>
-  <si>
-    <t>Section Habitus et modes de vie</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.historiqueDesActes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-historique-des-actes
-</t>
-  </si>
-  <si>
-    <t>Section Historique des actes</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.historiqueDesGrossesses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-historique-des-grossesses
-</t>
-  </si>
-  <si>
-    <t>Section Historique des grossesses</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.planSoins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-plan-soins
-</t>
-  </si>
-  <si>
-    <t>Section Plan de Soins</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.pointsDeVigilancesNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-points-de-vigilances-non-code
-</t>
-  </si>
-  <si>
-    <t>Section Points de Vigilances non code</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.prescriptionDispositifsMedicaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-dispositifs-medicaux
-</t>
-  </si>
-  <si>
-    <t>Section Prescription de dispositifs médicaux</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.prescriptionMedicaments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-medicaments
-</t>
-  </si>
-  <si>
-    <t>Section Prescription médicaments</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.problemesActifs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-problemes-actifs
-</t>
-  </si>
-  <si>
-    <t>Section Problemès Actifs</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.raisonRecommandationNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-raison-recommandation-non-code
-</t>
-  </si>
-  <si>
-    <t>Section Raison de la recommandation (non Codé)</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.raisonRecommandation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-raison-recommandation
-</t>
-  </si>
-  <si>
-    <t>Section Raison de la recommandation</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultatsLaboratoireBiologieSecondeIntention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-laboratoire-biologie-seconde-intention
-</t>
-  </si>
-  <si>
-    <t>Section Résultats de laboratoire de biologie de seconde intention</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultatsEvenements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-evenements
-</t>
-  </si>
-  <si>
-    <t>Section Resultats d'évenements</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultatsExamensNonCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-examens-non-code
-</t>
-  </si>
-  <si>
-    <t>Section Resultats d'xamens (non Codée)</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultatsExamens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-examens
-</t>
-  </si>
-  <si>
-    <t>Section Résultats d'examens</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats
-</t>
-  </si>
-  <si>
-    <t>Section Resultats</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.signesVitaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-signes-vitaux
-</t>
-  </si>
-  <si>
-    <t>Section Signes vitaux</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.statutDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-statut-document
-</t>
-  </si>
-  <si>
-    <t>Section Statut du document</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.statutFonctionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-statut-fonctionnel
-</t>
-  </si>
-  <si>
-    <t>Section Statut fonctionnel</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.traitements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitements
-</t>
-  </si>
-  <si>
-    <t>Section Traitement</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.traitementSortie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement-sortie
+    <t>Section Résultats d'événements</t>
+  </si>
+  <si>
+    <t>fr-lm-corps-document.hospitalDischargeMedications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-hospital-discharge-medications
 </t>
   </si>
   <si>
@@ -698,26 +678,6 @@
   </si>
   <si>
     <t>Section Traitements administrés</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.vaccinations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-vaccinations
-</t>
-  </si>
-  <si>
-    <t>Section Vaccinations</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.resultatsExamenImagerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-examen-imagerie
-</t>
-  </si>
-  <si>
-    <t>Section Résultats d'examen d'imagerie</t>
   </si>
 </sst>
 </file>
@@ -1019,11 +979,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.4765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="54.4765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.33984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1032,7 +992,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.7421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1053,7 +1013,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="54.4765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.33984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -5569,406 +5529,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
